--- a/data/trans_bre/P5B_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Clase-trans_bre.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,09</t>
+          <t>-1,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>146,56%</t>
+          <t>146,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 6,29</t>
+          <t>-2,5; 6,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 8,49</t>
+          <t>-1,64; 8,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 0,0</t>
+          <t>-3,91; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 4,85</t>
+          <t>-5,2; 4,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 5,05</t>
+          <t>-2,71; 5,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,51</t>
+          <t>-2,48; 1,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,71</t>
+          <t>-6,79; 0,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,0</t>
+          <t>-3,94; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,58</t>
+          <t>-2,03; 3,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 0,0</t>
+          <t>-8,86; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-9,35%</t>
+          <t>-8,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 6,32</t>
+          <t>-0,83; 6,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,0</t>
+          <t>-2,87; 1,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,12</t>
+          <t>-3,09; 2,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 41,92</t>
+          <t>-0,85; 39,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 456,32</t>
+          <t>-28,7; 627,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 478,57</t>
+          <t>-100,0; 323,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-82,63; 182,1</t>
+          <t>-76,47; 248,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 8,23</t>
+          <t>-4,01; 8,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,24</t>
+          <t>-1,32; 5,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,25</t>
+          <t>-1,03; 4,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,82; 331,06</t>
+          <t>-66,39; 405,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,97; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 2,91</t>
+          <t>-7,89; 2,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 6,12</t>
+          <t>-4,36; 6,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,37</t>
+          <t>0,92; 8,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,82; 205,7</t>
+          <t>-90,63; 168,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 725,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1237,17 +1237,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>259,25%</t>
+          <t>258,87%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,55</t>
+          <t>-0,87; 2,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,83</t>
+          <t>-0,78; 1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,82</t>
+          <t>-0,3; 1,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 16,93</t>
+          <t>-0,98; 18,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 117,64</t>
+          <t>-23,72; 122,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,01; 183,24</t>
+          <t>-41,49; 182,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 270,09</t>
+          <t>-26,95; 283,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-70,53; 2459,64</t>
+          <t>-67,7; 1822,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5B_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Clase-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 6,07</t>
+          <t>-2,21; 6,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 8,62</t>
+          <t>-1,54; 8,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,0</t>
+          <t>-3,74; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 4,21</t>
+          <t>-5,32; 4,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 5,35</t>
+          <t>-2,74; 4,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,51</t>
+          <t>-2,46; 1,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 0,69</t>
+          <t>-6,56; 0,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 324,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,0</t>
+          <t>-3,31; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,61</t>
+          <t>-2,0; 4,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 0,0</t>
+          <t>-11,28; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,42</t>
+          <t>-0,68; 6,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,82</t>
+          <t>-2,7; 1,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,43</t>
+          <t>-2,84; 2,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 39,03</t>
+          <t>-0,95; 40,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 627,34</t>
+          <t>-27,99; 573,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 323,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-76,47; 248,27</t>
+          <t>-74,82; 270,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 8,08</t>
+          <t>-3,37; 8,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 5,22</t>
+          <t>-1,49; 5,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,31</t>
+          <t>-1,32; 4,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-66,39; 405,36</t>
+          <t>-58,87; 389,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-84,97; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 2,15</t>
+          <t>-7,76; 2,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 6,11</t>
+          <t>-4,83; 6,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,12</t>
+          <t>0,93; 8,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 0,0</t>
+          <t>-5,14; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,63; 168,28</t>
+          <t>-100,0; 157,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 614,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,74</t>
+          <t>-0,95; 2,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,75</t>
+          <t>-0,86; 1,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,86</t>
+          <t>-0,52; 1,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 18,88</t>
+          <t>-1,05; 17,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 122,0</t>
+          <t>-24,79; 122,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 182,5</t>
+          <t>-45,79; 186,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 283,78</t>
+          <t>-34,35; 290,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-67,7; 1822,76</t>
+          <t>-72,15; 1894,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5B_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 6,21</t>
+          <t>-2,81; 6,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 8,56</t>
+          <t>-1,79; 8,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,0</t>
+          <t>-4,19; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-1,9</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-73,08%</t>
+          <t>-70,72%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 4,27</t>
+          <t>-4,81; 4,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 4,93</t>
+          <t>-2,7; 5,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,52</t>
+          <t>-2,49; 1,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 0,69</t>
+          <t>-6,17; 0,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 324,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,23</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,0</t>
+          <t>-4,13; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,59</t>
+          <t>-2,03; 3,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 0,0</t>
+          <t>-9,85; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,8</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1629,82%</t>
+          <t>149,02%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 6,94</t>
+          <t>-0,74; 6,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,87</t>
+          <t>-2,79; 2,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,41</t>
+          <t>-2,91; 2,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 40,82</t>
+          <t>-0,97; 7,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,99; 573,11</t>
+          <t>-27,92; 456,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 478,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,82; 270,41</t>
+          <t>-77,7; 220,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>120,93%</t>
+          <t>118,81%</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 8,34</t>
+          <t>-3,68; 8,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 5,41</t>
+          <t>-1,66; 5,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,11</t>
+          <t>-1,01; 4,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,87; 389,88</t>
+          <t>-59,82; 331,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 2,76</t>
+          <t>-7,54; 2,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 6,02</t>
+          <t>-4,32; 6,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,06</t>
+          <t>0,93; 7,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,0</t>
+          <t>-4,7; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 157,88</t>
+          <t>-91,82; 205,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 614,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>258,87%</t>
+          <t>-19,08%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,73</t>
+          <t>-0,9; 2,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,78</t>
+          <t>-0,91; 1,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,78</t>
+          <t>-0,48; 1,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 17,15</t>
+          <t>-1,26; 1,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 122,4</t>
+          <t>-24,72; 117,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-45,79; 186,62</t>
+          <t>-43,79; 170,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 290,78</t>
+          <t>-35,83; 315,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-72,15; 1894,31</t>
+          <t>-75,43; 203,52</t>
         </is>
       </c>
     </row>
